--- a/Agile/Unit_Test_Plan_v0.1.xlsx
+++ b/Agile/Unit_Test_Plan_v0.1.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24326"/>
-  <workbookPr defaultThemeVersion="166925"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://infosystechnologies-my.sharepoint.com/personal/kamaljeet_kaur01_ad_infosys_com1/Documents/Infosys/CC/Events/Oct 2021 - Mar 2022/CC2.0/Internship/Jan-Apr 2022/Artifacts/internship/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\GeethaJyothi\.gemini\antigravity\scratch\knowledge-retrieval-platform\Agile\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3B9D4FEA-5A3F-460B-9A40-165575443B6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{C3B83BB6-2AB9-4547-8541-9F6969E92BF1}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="15345" windowHeight="4830"/>
   </bookViews>
   <sheets>
     <sheet name="UT" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="162913"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -34,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="55">
   <si>
     <t>Actual Result</t>
   </si>
@@ -52,24 +51,164 @@
   </si>
   <si>
     <t>Sl: No:</t>
+  </si>
+  <si>
+    <t>Factual query classification</t>
+  </si>
+  <si>
+    <t>Submit a factual question to the query endpoint.</t>
+  </si>
+  <si>
+    <t>Query asks for a fact/definition.</t>
+  </si>
+  <si>
+    <t>Query type is classified as factual and routed to retrieval.</t>
+  </si>
+  <si>
+    <t>Pass</t>
+  </si>
+  <si>
+    <t>Procedural query classification</t>
+  </si>
+  <si>
+    <t>Submit a how-to question.</t>
+  </si>
+  <si>
+    <t>Query requests a procedure or steps.</t>
+  </si>
+  <si>
+    <t>Query type is classified as procedural and routed to retrieval.</t>
+  </si>
+  <si>
+    <t>Comparative query classification</t>
+  </si>
+  <si>
+    <t>Submit a comparison question.</t>
+  </si>
+  <si>
+    <t>Query asks for differences/similarities.</t>
+  </si>
+  <si>
+    <t>Query type is classified as comparative and routed to retrieval.</t>
+  </si>
+  <si>
+    <t>Ambiguous query classification</t>
+  </si>
+  <si>
+    <t>Submit an underspecified query such as 'Tell me about it.'</t>
+  </si>
+  <si>
+    <t>Query lacks sufficient context.</t>
+  </si>
+  <si>
+    <t>Query type is classified as ambiguous and normal retrieval is not performed.</t>
+  </si>
+  <si>
+    <t>Retrieval Agent semantic search</t>
+  </si>
+  <si>
+    <t>Submit a supported query against indexed documents.</t>
+  </si>
+  <si>
+    <t>Relevant knowledge exists in the vector index.</t>
+  </si>
+  <si>
+    <t>Relevant document chunks are returned.</t>
+  </si>
+  <si>
+    <t>Retrieval provenance</t>
+  </si>
+  <si>
+    <t>Inspect returned retrieval metadata.</t>
+  </si>
+  <si>
+    <t>A relevant chunk is retrieved.</t>
+  </si>
+  <si>
+    <t>Source/provenance information is available with the retrieved result.</t>
+  </si>
+  <si>
+    <t>Response generation</t>
+  </si>
+  <si>
+    <t>Submit a supported query through the complete pipeline.</t>
+  </si>
+  <si>
+    <t>Relevant context is available.</t>
+  </si>
+  <si>
+    <t>A natural-language response is generated from retrieved context.</t>
+  </si>
+  <si>
+    <t>Grounded response validation</t>
+  </si>
+  <si>
+    <t>Submit a query with insufficient supporting retrieval.</t>
+  </si>
+  <si>
+    <t>Retrieved evidence does not sufficiently support the query.</t>
+  </si>
+  <si>
+    <t>System avoids treating unsupported content as valid grounding.</t>
+  </si>
+  <si>
+    <t>Out-of-domain handling</t>
+  </si>
+  <si>
+    <t>Submit a question outside the uploaded knowledge base.</t>
+  </si>
+  <si>
+    <t>No sufficiently relevant evidence is available.</t>
+  </si>
+  <si>
+    <t>System returns an insufficient-information response instead of an unsupported answer.</t>
+  </si>
+  <si>
+    <t>Orchestrator sequence</t>
+  </si>
+  <si>
+    <t>Submit a normal supported query.</t>
+  </si>
+  <si>
+    <t>All required agents are available.</t>
+  </si>
+  <si>
+    <t>Understanding → Retrieval → Response sequence is coordinated correctly.</t>
+  </si>
+  <si>
+    <t>Ambiguous routing</t>
+  </si>
+  <si>
+    <t>Submit an ambiguous query.</t>
+  </si>
+  <si>
+    <t>Query Understanding returns ambiguous.</t>
+  </si>
+  <si>
+    <t>Orchestrator skips normal retrieval/response generation path and returns the M2 guidance response.</t>
+  </si>
+  <si>
+    <t>End-to-end UI/API integration</t>
+  </si>
+  <si>
+    <t>Submit queries through the application UI.</t>
+  </si>
+  <si>
+    <t>Application and backend are running.</t>
+  </si>
+  <si>
+    <t>Classification, pipeline stages, answer and source/confidence information are displayed correctly.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
       <family val="2"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color indexed="56"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <b/>
@@ -78,6 +217,18 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF003366"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="3">
@@ -94,7 +245,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -117,18 +268,34 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -442,8 +609,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF95B16C-182C-4757-B929-A728708A2DB0}">
-  <dimension ref="A1:F6"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:F16"/>
   <sheetFormatPr defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9.140625" customWidth="1"/>
@@ -453,65 +620,289 @@
     <col min="6" max="6" width="15.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="31.5" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:6" ht="32.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A2" s="1"/>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-    </row>
-    <row r="3" spans="1:6" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A3" s="1"/>
-      <c r="B3" s="1"/>
-      <c r="C3" s="1"/>
-      <c r="D3" s="1"/>
-      <c r="E3" s="1"/>
-      <c r="F3" s="1"/>
-    </row>
-    <row r="4" spans="1:6" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A4" s="1"/>
-      <c r="B4" s="1"/>
-      <c r="C4" s="1"/>
-      <c r="D4" s="1"/>
-      <c r="E4" s="1"/>
-      <c r="F4" s="1"/>
-    </row>
-    <row r="5" spans="1:6" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A5" s="1"/>
-      <c r="B5" s="1"/>
-      <c r="C5" s="1"/>
-      <c r="D5" s="1"/>
-      <c r="E5" s="1"/>
-      <c r="F5" s="1"/>
-    </row>
-    <row r="6" spans="1:6" ht="15.75" x14ac:dyDescent="0.2">
-      <c r="A6" s="1"/>
-      <c r="B6" s="1"/>
-      <c r="C6" s="1"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
+    <row r="2" spans="1:6" ht="79.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="79.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="2">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="79.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="2">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="95.25" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="2">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="F5" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="79.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="2">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A7" s="3">
+        <v>6</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="F7" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A8" s="3">
+        <v>7</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="F8" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A9" s="3">
+        <v>8</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="F9" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A10" s="3">
+        <v>9</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="F10" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A11" s="3">
+        <v>10</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>46</v>
+      </c>
+      <c r="F11" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A12" s="3">
+        <v>11</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="F12" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A13" s="3">
+        <v>12</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>52</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>54</v>
+      </c>
+      <c r="F13" s="3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A14" s="3"/>
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+      <c r="D14" s="3"/>
+      <c r="E14" s="3"/>
+      <c r="F14" s="3"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A15" s="3"/>
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+      <c r="D15" s="3"/>
+      <c r="E15" s="3"/>
+      <c r="F15" s="3"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
+      <c r="A16" s="3"/>
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+      <c r="D16" s="3"/>
+      <c r="E16" s="3"/>
+      <c r="F16" s="3"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Agile/Unit_Test_Plan_v0.1.xlsx
+++ b/Agile/Unit_Test_Plan_v0.1.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="55">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="67">
   <si>
     <t>Actual Result</t>
   </si>
@@ -59,12 +59,6 @@
     <t>Submit a factual question to the query endpoint.</t>
   </si>
   <si>
-    <t>Query asks for a fact/definition.</t>
-  </si>
-  <si>
-    <t>Query type is classified as factual and routed to retrieval.</t>
-  </si>
-  <si>
     <t>Pass</t>
   </si>
   <si>
@@ -74,24 +68,12 @@
     <t>Submit a how-to question.</t>
   </si>
   <si>
-    <t>Query requests a procedure or steps.</t>
-  </si>
-  <si>
-    <t>Query type is classified as procedural and routed to retrieval.</t>
-  </si>
-  <si>
     <t>Comparative query classification</t>
   </si>
   <si>
     <t>Submit a comparison question.</t>
   </si>
   <si>
-    <t>Query asks for differences/similarities.</t>
-  </si>
-  <si>
-    <t>Query type is classified as comparative and routed to retrieval.</t>
-  </si>
-  <si>
     <t>Ambiguous query classification</t>
   </si>
   <si>
@@ -101,12 +83,6 @@
     <t>Query lacks sufficient context.</t>
   </si>
   <si>
-    <t>Query type is classified as ambiguous and normal retrieval is not performed.</t>
-  </si>
-  <si>
-    <t>Retrieval Agent semantic search</t>
-  </si>
-  <si>
     <t>Submit a supported query against indexed documents.</t>
   </si>
   <si>
@@ -116,18 +92,6 @@
     <t>Relevant document chunks are returned.</t>
   </si>
   <si>
-    <t>Retrieval provenance</t>
-  </si>
-  <si>
-    <t>Inspect returned retrieval metadata.</t>
-  </si>
-  <si>
-    <t>A relevant chunk is retrieved.</t>
-  </si>
-  <si>
-    <t>Source/provenance information is available with the retrieved result.</t>
-  </si>
-  <si>
     <t>Response generation</t>
   </si>
   <si>
@@ -137,67 +101,139 @@
     <t>Relevant context is available.</t>
   </si>
   <si>
-    <t>A natural-language response is generated from retrieved context.</t>
-  </si>
-  <si>
-    <t>Grounded response validation</t>
-  </si>
-  <si>
-    <t>Submit a query with insufficient supporting retrieval.</t>
-  </si>
-  <si>
-    <t>Retrieved evidence does not sufficiently support the query.</t>
-  </si>
-  <si>
-    <t>System avoids treating unsupported content as valid grounding.</t>
-  </si>
-  <si>
-    <t>Out-of-domain handling</t>
-  </si>
-  <si>
-    <t>Submit a question outside the uploaded knowledge base.</t>
-  </si>
-  <si>
-    <t>No sufficiently relevant evidence is available.</t>
-  </si>
-  <si>
-    <t>System returns an insufficient-information response instead of an unsupported answer.</t>
-  </si>
-  <si>
-    <t>Orchestrator sequence</t>
-  </si>
-  <si>
-    <t>Submit a normal supported query.</t>
-  </si>
-  <si>
-    <t>All required agents are available.</t>
-  </si>
-  <si>
-    <t>Understanding → Retrieval → Response sequence is coordinated correctly.</t>
-  </si>
-  <si>
-    <t>Ambiguous routing</t>
-  </si>
-  <si>
-    <t>Submit an ambiguous query.</t>
-  </si>
-  <si>
-    <t>Query Understanding returns ambiguous.</t>
-  </si>
-  <si>
-    <t>Orchestrator skips normal retrieval/response generation path and returns the M2 guidance response.</t>
-  </si>
-  <si>
-    <t>End-to-end UI/API integration</t>
-  </si>
-  <si>
-    <t>Submit queries through the application UI.</t>
-  </si>
-  <si>
-    <t>Application and backend are running.</t>
-  </si>
-  <si>
-    <t>Classification, pipeline stages, answer and source/confidence information are displayed correctly.</t>
+    <t>Query asks for a fact or definition.</t>
+  </si>
+  <si>
+    <t>Query is classified as factual and routed to retrieval.</t>
+  </si>
+  <si>
+    <t>Query requests steps or a procedure.</t>
+  </si>
+  <si>
+    <t>Query is classified as procedural and routed correctly.</t>
+  </si>
+  <si>
+    <t>Query asks for differences or similarities.</t>
+  </si>
+  <si>
+    <t>Query is classified as comparative and routed correctly.</t>
+  </si>
+  <si>
+    <t>Query is classified as ambiguous and clarification is requested.</t>
+  </si>
+  <si>
+    <t>Retrieval semantic search</t>
+  </si>
+  <si>
+    <t>Retrieval relevance filtering</t>
+  </si>
+  <si>
+    <t>Submit an unrelated query.</t>
+  </si>
+  <si>
+    <t>No sufficiently relevant knowledge is available.</t>
+  </si>
+  <si>
+    <t>Low-relevance results are filtered instead of being used as evidence.</t>
+  </si>
+  <si>
+    <t>Grounded natural-language response is generated.</t>
+  </si>
+  <si>
+    <t>Source provenance</t>
+  </si>
+  <si>
+    <t>Inspect response metadata after retrieval.</t>
+  </si>
+  <si>
+    <t>A document chunk is used.</t>
+  </si>
+  <si>
+    <t>Source/provenance information is available.</t>
+  </si>
+  <si>
+    <t>Multi-agent orchestration</t>
+  </si>
+  <si>
+    <t>Submit factual, procedural, comparative and ambiguous queries.</t>
+  </si>
+  <si>
+    <t>Different query types require different routing.</t>
+  </si>
+  <si>
+    <t>Orchestrator routes each query to the appropriate agent flow.</t>
+  </si>
+  <si>
+    <t>Clarification Agent</t>
+  </si>
+  <si>
+    <t>Submit an ambiguous or incomplete query.</t>
+  </si>
+  <si>
+    <t>Required context is missing.</t>
+  </si>
+  <si>
+    <t>System asks a relevant clarification question.</t>
+  </si>
+  <si>
+    <t>Conversation memory</t>
+  </si>
+  <si>
+    <t>Ask a follow-up question referring to the previous turn.</t>
+  </si>
+  <si>
+    <t>Previous conversation contains required context.</t>
+  </si>
+  <si>
+    <t>System uses the previous turn and answers the follow-up correctly.</t>
+  </si>
+  <si>
+    <t>Voice input</t>
+  </si>
+  <si>
+    <t>Speak a query through the UI.</t>
+  </si>
+  <si>
+    <t>Browser supports speech recognition and permission is granted.</t>
+  </si>
+  <si>
+    <t>Recognized speech is inserted as a query and processed.</t>
+  </si>
+  <si>
+    <t>Voice fallback</t>
+  </si>
+  <si>
+    <t>Attempt voice input where recognition is unavailable.</t>
+  </si>
+  <si>
+    <t>Speech recognition is unavailable or denied.</t>
+  </si>
+  <si>
+    <t>User can continue using text input without breaking the flow.</t>
+  </si>
+  <si>
+    <t>Knowledge-gap logging</t>
+  </si>
+  <si>
+    <t>Submit an unanswered or low-confidence query.</t>
+  </si>
+  <si>
+    <t>Response confidence is below the configured threshold or no answer is available.</t>
+  </si>
+  <si>
+    <t>Query is recorded for analytics and knowledge-gap analysis.</t>
+  </si>
+  <si>
+    <t>Three-domain end-to-end test</t>
+  </si>
+  <si>
+    <t>Run representative queries from three distinct knowledge domains.</t>
+  </si>
+  <si>
+    <t>Each domain has indexed documents.</t>
+  </si>
+  <si>
+    <t>Retrieval, agent collaboration, response generation, voice and memory work across all domains.</t>
   </si>
 </sst>
 </file>
@@ -220,13 +256,13 @@
     </font>
     <font>
       <sz val="12"/>
-      <color rgb="FF003366"/>
+      <color theme="4" tint="-0.249977111117893"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
-      <color rgb="FF000000"/>
+      <color theme="4" tint="-0.249977111117893"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
@@ -287,15 +323,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -644,265 +688,301 @@
       <c r="A2" s="2">
         <v>1</v>
       </c>
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>9</v>
+      <c r="D2" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>23</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" ht="79.5" thickBot="1" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="63.75" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>14</v>
+      <c r="B3" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>25</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="4" spans="1:6" ht="79.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" s="2" t="s">
-        <v>18</v>
+      <c r="B4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>27</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="95.25" thickBot="1" x14ac:dyDescent="0.25">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="79.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>21</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>22</v>
+      <c r="B5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D5" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="3" t="s">
+        <v>28</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:6" ht="79.5" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="2" t="s">
-        <v>24</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>26</v>
+      <c r="B6" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>18</v>
       </c>
       <c r="F6" s="2" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="51.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="4">
+        <v>6</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="C7" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="E7" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="64.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="4">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C8" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="51.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A9" s="4">
+        <v>8</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="F9" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="64.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A10" s="4">
+        <v>9</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="F10" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="51.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="4">
         <v>10</v>
       </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A7" s="3">
-        <v>6</v>
-      </c>
-      <c r="B7" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>28</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>29</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>30</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A8" s="3">
-        <v>7</v>
-      </c>
-      <c r="B8" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A9" s="3">
-        <v>8</v>
-      </c>
-      <c r="B9" s="3" t="s">
-        <v>35</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>36</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A10" s="3">
-        <v>9</v>
-      </c>
-      <c r="B10" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C10" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>42</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A11" s="3">
-        <v>10</v>
-      </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="C11" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="D11" s="3" t="s">
+      <c r="D11" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="E11" s="3" t="s">
+      <c r="E11" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="F11" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A12" s="3">
+      <c r="F11" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" ht="51.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="4">
         <v>11</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="E12" s="3" t="s">
+      <c r="E12" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="F12" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A13" s="3">
+      <c r="F12" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="64.5" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="4">
         <v>12</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="E13" s="3" t="s">
+      <c r="E13" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="F13" s="3" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A14" s="3"/>
-      <c r="B14" s="3"/>
-      <c r="C14" s="3"/>
-      <c r="D14" s="3"/>
-      <c r="E14" s="3"/>
-      <c r="F14" s="3"/>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A15" s="3"/>
-      <c r="B15" s="3"/>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3"/>
-      <c r="E15" s="3"/>
-      <c r="F15" s="3"/>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A16" s="3"/>
-      <c r="B16" s="3"/>
-      <c r="C16" s="3"/>
-      <c r="D16" s="3"/>
-      <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
+      <c r="F13" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="51.75" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="4">
+        <v>13</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="90" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="4">
+        <v>14</v>
+      </c>
+      <c r="B15" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="C15" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>62</v>
+      </c>
+      <c r="F15" s="4" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="90" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="4">
+        <v>15</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C16" s="5" t="s">
+        <v>64</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="F16" s="4" t="s">
+        <v>8</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
